--- a/tasks_gradebook_v4.xlsx
+++ b/tasks_gradebook_v4.xlsx
@@ -721,11 +721,11 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>57.1</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23 19:45</t>
+          <t>2026-01-24 19:45</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="H2" s="3" t="n">
-        <v>48</v>
+        <v>65.5</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
@@ -747,11 +747,11 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 16:22</t>
+          <t>2026-02-20 16:22</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>67.3</v>
+        <v>83.7</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 19:38</t>
+          <t>2026-03-04 19:38</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>45.9</v>
+        <v>61.7</v>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
@@ -789,17 +789,17 @@
         <v>0</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>282.4</v>
+        <v>367</v>
       </c>
       <c r="V2" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>56.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>68.2</v>
+        <v>72.2</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>79.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 15:53</t>
+          <t>2026-02-03 15:53</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -856,11 +856,11 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>70</v>
+        <v>72.2</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 19:11</t>
+          <t>2026-02-18 19:11</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -869,11 +869,11 @@
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 15:02</t>
+          <t>2026-03-03 15:02</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>79.8</v>
+        <v>80.3</v>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
@@ -895,16 +895,16 @@
         </is>
       </c>
       <c r="T3" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>383.2</v>
+        <v>399.5</v>
       </c>
       <c r="V3" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 15:07</t>
+          <t>2026-01-21 15:07</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -952,11 +952,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>57.9</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 13:13</t>
+          <t>2026-02-06 13:13</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -965,11 +965,11 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>58.6</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 22:26</t>
+          <t>2026-02-18 22:26</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -978,11 +978,11 @@
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>57.6</v>
+        <v>69.2</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 19:49</t>
+          <t>2026-03-04 19:49</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
@@ -1007,17 +1007,17 @@
         <v>0</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>321.6</v>
+        <v>378.3</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>64.3</v>
+        <v>75.7</v>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>73.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 19:39</t>
+          <t>2026-01-21 19:39</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1061,11 +1061,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>80.7</v>
+        <v>72</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 12:46</t>
+          <t>2026-02-06 12:46</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -1074,11 +1074,11 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>77.7</v>
+        <v>69.5</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 16:34</t>
+          <t>2026-02-19 16:34</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -1087,11 +1087,11 @@
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 12:06</t>
+          <t>2026-03-05 12:06</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>81</v>
+        <v>73.5</v>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
         </is>
       </c>
       <c r="T5" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>401.2</v>
+        <v>354.9</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>80.2</v>
+        <v>71</v>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>51.9</v>
+        <v>59.3</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 17:01</t>
+          <t>2026-01-19 17:01</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1170,11 +1170,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>63.2</v>
+        <v>72.8</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 22:12</t>
+          <t>2026-02-03 22:12</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>67.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>71.7</v>
+        <v>85.5</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>73.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
@@ -1222,20 +1222,20 @@
         </is>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>327.9</v>
+        <v>391.1</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -1266,11 +1266,11 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>78.2</v>
+        <v>70.2</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 13:10</t>
+          <t>2026-01-20 13:10</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
@@ -1292,11 +1292,11 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>77.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 18:27</t>
+          <t>2026-02-18 18:27</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1305,11 +1305,11 @@
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 21:30</t>
+          <t>2026-03-03 21:30</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>76.8</v>
+        <v>71.5</v>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
@@ -1334,17 +1334,17 @@
         <v>0</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>385.7</v>
+        <v>352.6</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1375,11 +1375,11 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 13:07</t>
+          <t>2026-01-23 13:07</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1388,11 +1388,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>90.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 14:54</t>
+          <t>2026-02-05 14:54</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 15:15</t>
+          <t>2026-02-18 15:15</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>92.3</v>
+        <v>84</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>80.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
@@ -1440,20 +1440,20 @@
         </is>
       </c>
       <c r="T8" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>462.1</v>
+        <v>406.6</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>81.3</v>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -1484,11 +1484,11 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>65.5</v>
+        <v>63.3</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 20:34</t>
+          <t>2026-01-21 20:34</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>61.4</v>
+        <v>60.2</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 15:51</t>
+          <t>2026-02-05 15:51</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>68.2</v>
+        <v>68</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 15:43</t>
+          <t>2026-02-18 15:43</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1523,11 +1523,11 @@
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>79.5</v>
+        <v>80.3</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 13:37</t>
+          <t>2026-03-03 13:37</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>60.9</v>
+        <v>62.6</v>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
@@ -1552,13 +1552,13 @@
         <v>0</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>335.5</v>
+        <v>334.4</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>62.3</v>
+        <v>59.1</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>74.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>76.8</v>
+        <v>72.5</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>88.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>86.3</v>
+        <v>81</v>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
@@ -1661,17 +1661,17 @@
         <v>0</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>387.8</v>
+        <v>366.4</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -1702,11 +1702,11 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>66.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 11:34</t>
+          <t>2026-01-21 11:34</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1715,11 +1715,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 20:16</t>
+          <t>2026-02-06 20:16</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1728,11 +1728,11 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>85.2</v>
+        <v>85.5</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 16:31</t>
+          <t>2026-02-19 16:31</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>96.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -1770,13 +1770,13 @@
         <v>15</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="X11" s="4" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>70.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1824,11 +1824,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02 17:54</t>
+          <t>2026-02-03 17:54</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1837,11 +1837,11 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>63</v>
+        <v>77.8</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 12:02</t>
+          <t>2026-02-19 12:02</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>74.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>80.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
@@ -1876,20 +1876,20 @@
         </is>
       </c>
       <c r="T12" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>354.7</v>
+        <v>443.9</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t>C+</t>
+        <v>88.8</v>
+      </c>
+      <c r="X12" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>58.4</v>
+        <v>56.5</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1933,11 +1933,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>74.7</v>
+        <v>73.7</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 13:26</t>
+          <t>2026-02-04 13:26</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1946,11 +1946,11 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>72</v>
+        <v>71.8</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 11:53</t>
+          <t>2026-02-19 11:53</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1959,11 +1959,11 @@
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 20:53</t>
+          <t>2026-03-02 20:53</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>72</v>
+        <v>73.3</v>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
@@ -1988,13 +1988,13 @@
         <v>0</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>346.5</v>
+        <v>345.2</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>69.3</v>
+        <v>69</v>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>81.5</v>
+        <v>81.8</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>74.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -2068,11 +2068,11 @@
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 19:10</t>
+          <t>2026-03-03 19:10</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>5</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>396.3</v>
+        <v>396.5</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>500</v>
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>83.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>66.90000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>81.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
@@ -2203,20 +2203,20 @@
         </is>
       </c>
       <c r="T15" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>386.4</v>
+        <v>419.7</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>77.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -2247,11 +2247,11 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>57.8</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 10:29</t>
+          <t>2026-01-21 10:29</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2260,11 +2260,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>94.2</v>
+        <v>70.3</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 13:57</t>
+          <t>2026-02-03 13:57</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>54.9</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>90.8</v>
+        <v>68.2</v>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>88.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
@@ -2312,20 +2312,20 @@
         </is>
       </c>
       <c r="T16" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>449</v>
+        <v>317.8</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>63.6</v>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>61.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>63.4</v>
+        <v>77.7</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>82.5</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>78.2</v>
+        <v>94.7</v>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>57.1</v>
+        <v>74.8</v>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
@@ -2421,20 +2421,20 @@
         </is>
       </c>
       <c r="T17" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>342.8</v>
+        <v>434.7</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>86.90000000000001</v>
+      </c>
+      <c r="X17" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>80</v>
+        <v>75.8</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2478,11 +2478,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 20:48</t>
+          <t>2026-02-04 20:48</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2504,11 +2504,11 @@
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 14:08</t>
+          <t>2026-03-03 14:08</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>79.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
@@ -2530,20 +2530,20 @@
         </is>
       </c>
       <c r="T18" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>406.5</v>
+        <v>381.5</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>81.3</v>
+        <v>76.3</v>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -2574,11 +2574,11 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>58.7</v>
+        <v>69.8</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 16:01</t>
+          <t>2026-01-23 16:01</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>69.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>69.3</v>
+        <v>79.5</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
@@ -2642,17 +2642,17 @@
         <v>0</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>332.8</v>
+        <v>383.6</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>58</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 22:24</t>
+          <t>2026-01-20 22:24</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2696,11 +2696,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>74.7</v>
+        <v>54.2</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 09:22</t>
+          <t>2026-02-05 09:22</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>80.5</v>
+        <v>63.2</v>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
@@ -2748,20 +2748,20 @@
         </is>
       </c>
       <c r="T20" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>422.1</v>
+        <v>322.6</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>87.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>85.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
@@ -2818,11 +2818,11 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>61.3</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 22:51</t>
+          <t>2026-02-17 22:51</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -2831,11 +2831,11 @@
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 19:23</t>
+          <t>2026-03-05 19:23</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
@@ -2857,20 +2857,20 @@
         </is>
       </c>
       <c r="T21" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>423.1</v>
+        <v>351.3</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -2901,11 +2901,11 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>52.2</v>
+        <v>60.2</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 11:27</t>
+          <t>2026-01-22 07:55</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2913,73 +2913,73 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="H22" s="6" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-06 20:42</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
+      <c r="H22" s="3" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-05 19:13</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-19 13:35</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-06 20:12</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="K22" s="6" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-21 00:36</t>
-        </is>
-      </c>
-      <c r="M22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-20 20:48</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 13:59</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-19 00:57</t>
-        </is>
-      </c>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
         </is>
       </c>
       <c r="T22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>238.8</v>
+        <v>311.6</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="X22" s="7" t="inlineStr">
-        <is>
-          <t>F</t>
+        <v>62.3</v>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -3010,11 +3010,11 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>58.1</v>
+        <v>45.2</v>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>2026-01-24 00:42</t>
+          <t>2026-01-23 20:18</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -3022,51 +3022,51 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H23" s="6" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-07 00:42</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="H23" s="3" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-05 11:07</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-20 18:12</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="K23" s="3" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-19 15:37</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:34</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N23" s="6" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:36</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>82.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 10:11</t>
+          <t>2026-03-19 20:09</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -3078,17 +3078,17 @@
         <v>0</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>356.9</v>
+        <v>303</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>60.6</v>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -3118,82 +3118,82 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-23 19:48</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="E24" s="3" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-22 19:57</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-05 08:10</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-20 05:56</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-04 23:24</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-20 18:36</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H24" s="3" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 06:56</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>77.7</v>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-19 18:42</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="N24" s="6" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="O24" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-07 01:42</t>
-        </is>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-20 03:39</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
       <c r="T24" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>356.4</v>
+        <v>361</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>71.3</v>
+        <v>72.2</v>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
@@ -3227,38 +3227,38 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E25" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 01:48</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 12:29</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="E25" s="6" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:12</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-06 19:00</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>56.8</v>
+        <v>72.7</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 08:43</t>
+          <t>2026-02-19 08:01</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -3267,11 +3267,11 @@
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>76.5</v>
+        <v>71.8</v>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 00:39</t>
+          <t>2026-03-06 04:45</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -3280,11 +3280,11 @@
         </is>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>89.7</v>
+        <v>83</v>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 10:14</t>
+          <t>2026-03-20 04:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -3293,20 +3293,20 @@
         </is>
       </c>
       <c r="T25" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>389.5</v>
+        <v>328.9</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -3337,11 +3337,11 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23 03:11</t>
+          <t>2026-01-23 14:26</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -3349,73 +3349,73 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="H26" s="6" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-07 00:48</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
+      <c r="H26" s="3" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-06 15:06</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-20 22:12</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-19 14:01</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-06 07:06</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-19 18:16</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N26" s="6" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:42</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:42</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="T26" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>315.2</v>
+        <v>257</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t>D+</t>
+        <v>51.4</v>
+      </c>
+      <c r="X26" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -3446,11 +3446,11 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>95.3</v>
+        <v>70.8</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 23:13</t>
+          <t>2026-01-22 15:49</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -3459,11 +3459,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>78.5</v>
+        <v>80.8</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 22:51</t>
+          <t>2026-02-05 09:44</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -3472,11 +3472,11 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 15:08</t>
+          <t>2026-02-19 01:12</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -3485,11 +3485,11 @@
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 01:22</t>
+          <t>2026-03-05 11:02</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3498,11 +3498,11 @@
         </is>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>96.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 20:17</t>
+          <t>2026-03-18 23:35</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -3514,17 +3514,17 @@
         <v>20</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>482.7</v>
+        <v>424.2</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="X27" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>84.8</v>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -3554,25 +3554,25 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-23 19:24</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="E28" s="3" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-22 14:56</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>54.3</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 23:00</t>
+          <t>2026-02-04 22:34</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -3581,11 +3581,11 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>77.7</v>
+        <v>53.2</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 22:08</t>
+          <t>2026-02-19 09:19</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -3594,11 +3594,11 @@
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>94.8</v>
+        <v>71.2</v>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 01:24</t>
+          <t>2026-03-05 16:46</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3607,11 +3607,11 @@
         </is>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>94.3</v>
+        <v>85.7</v>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 14:07</t>
+          <t>2026-03-19 12:29</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -3620,20 +3620,20 @@
         </is>
       </c>
       <c r="T28" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>416.5</v>
+        <v>350.9</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>83.3</v>
+        <v>70.2</v>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -3663,51 +3663,51 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E29" s="6" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-24 00:36</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="E29" s="3" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-22 21:25</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-06 22:00</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H29" s="6" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-07 00:54</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
+      <c r="K29" s="6" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-21 16:36</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-19 21:42</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
       <c r="N29" s="6" t="n">
-        <v>55.1</v>
+        <v>41.2</v>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>2026-03-07 00:48</t>
+          <t>2026-03-06 18:12</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
@@ -3716,11 +3716,11 @@
         </is>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>88.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 02:55</t>
+          <t>2026-03-19 21:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -3732,17 +3732,17 @@
         <v>0</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>340</v>
+        <v>251.8</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>50.4</v>
+      </c>
+      <c r="X29" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -3773,11 +3773,11 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 12:02</t>
+          <t>2026-01-22 07:32</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -3786,11 +3786,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>71</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 07:25</t>
+          <t>2026-02-06 02:24</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -3798,25 +3798,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K30" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-19 19:10</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="K30" s="6" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-20 18:54</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>85.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 02:43</t>
+          <t>2026-03-05 13:54</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -3825,11 +3825,11 @@
         </is>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 13:06</t>
+          <t>2026-03-19 17:08</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -3838,20 +3838,20 @@
         </is>
       </c>
       <c r="T30" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>427.8</v>
+        <v>354.4</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="X30" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -3881,51 +3881,51 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-24 00:54</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="E31" s="3" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-22 14:27</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-07 11:00</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H31" s="3" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 06:03</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="L31" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-20 22:48</t>
-        </is>
-      </c>
-      <c r="M31" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="K31" s="3" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-20 07:07</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>97.2</v>
+        <v>81.8</v>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 09:42</t>
+          <t>2026-03-05 16:56</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -3934,11 +3934,11 @@
         </is>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>87.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 23:00</t>
+          <t>2026-03-18 12:19</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -3947,16 +3947,16 @@
         </is>
       </c>
       <c r="T31" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>362.1</v>
+        <v>374.4</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
@@ -3991,11 +3991,11 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>62.3</v>
+        <v>78.7</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23 07:06</t>
+          <t>2026-01-22 04:09</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -4004,11 +4004,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>52.5</v>
+        <v>83.3</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 16:47</t>
+          <t>2026-02-06 05:42</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -4016,25 +4016,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K32" s="6" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="L32" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-21 00:18</t>
-        </is>
-      </c>
-      <c r="M32" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="K32" s="3" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-19 12:37</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>59</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 12:01</t>
+          <t>2026-03-06 03:02</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -4042,34 +4042,34 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-20 20:24</t>
-        </is>
-      </c>
-      <c r="S32" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q32" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19 19:57</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T32" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>256.9</v>
+        <v>424.9</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="X32" s="7" t="inlineStr">
-        <is>
-          <t>F</t>
+        <v>85</v>
+      </c>
+      <c r="X32" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -4100,11 +4100,11 @@
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>27.7</v>
+        <v>56.3</v>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 23:54</t>
+          <t>2026-01-23 21:36</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -4112,73 +4112,73 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H33" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-06 19:30</t>
-        </is>
-      </c>
-      <c r="J33" s="6" t="inlineStr">
+      <c r="H33" s="3" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-05 20:29</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-20 18:00</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="K33" s="6" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="L33" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-21 09:48</t>
-        </is>
-      </c>
-      <c r="M33" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="N33" s="6" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="O33" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 20:12</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-20 23:48</t>
-        </is>
-      </c>
-      <c r="S33" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="N33" s="3" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-05 16:22</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-20 05:30</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T33" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>212.3</v>
+        <v>340.8</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="X33" s="7" t="inlineStr">
-        <is>
-          <t>F</t>
+        <v>68.2</v>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -4209,11 +4209,11 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>58</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 02:28</t>
+          <t>2026-01-22 10:46</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -4222,11 +4222,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>51.6</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 09:29</t>
+          <t>2026-02-06 04:53</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -4235,11 +4235,11 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>62.2</v>
+        <v>71.5</v>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 04:54</t>
+          <t>2026-02-19 04:48</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -4248,11 +4248,11 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>54.4</v>
+        <v>62.9</v>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 14:31</t>
+          <t>2026-03-05 14:30</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4261,11 +4261,11 @@
         </is>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>60.5</v>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 20:47</t>
+          <t>2026-03-18 19:34</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -4274,20 +4274,20 @@
         </is>
       </c>
       <c r="T34" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>320.6</v>
+        <v>325.9</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -4318,11 +4318,11 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>42.2</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 22:08</t>
+          <t>2026-01-22 09:29</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -4330,25 +4330,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="H35" s="3" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 16:09</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="H35" s="6" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-06 21:30</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>63.1</v>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 21:27</t>
+          <t>2026-02-20 03:22</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -4357,11 +4357,11 @@
         </is>
       </c>
       <c r="N35" s="6" t="n">
-        <v>36.2</v>
+        <v>41.3</v>
       </c>
       <c r="O35" s="6" t="inlineStr">
         <is>
-          <t>2026-03-06 23:54</t>
+          <t>2026-03-06 21:06</t>
         </is>
       </c>
       <c r="P35" s="6" t="inlineStr">
@@ -4370,11 +4370,11 @@
         </is>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>64.90000000000001</v>
+        <v>50.4</v>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20 19:48</t>
+          <t>2026-03-20 19:36</t>
         </is>
       </c>
       <c r="S35" s="6" t="inlineStr">
@@ -4386,17 +4386,17 @@
         <v>0</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>380.5</v>
+        <v>236.7</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>47.3</v>
+      </c>
+      <c r="X35" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -4427,11 +4427,11 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>64.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 10:30</t>
+          <t>2026-01-23 04:32</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -4440,11 +4440,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>70.2</v>
+        <v>59.8</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 11:26</t>
+          <t>2026-02-05 23:20</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -4453,11 +4453,11 @@
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 17:44</t>
+          <t>2026-02-20 09:02</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -4465,25 +4465,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-06 07:33</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N36" s="6" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 17:06</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>72</v>
+        <v>81.3</v>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 23:51</t>
+          <t>2026-03-19 18:19</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -4492,20 +4492,20 @@
         </is>
       </c>
       <c r="T36" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>365.3</v>
+        <v>323.5</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -4536,11 +4536,11 @@
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>61.2</v>
+        <v>45.7</v>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>2026-01-24 01:42</t>
+          <t>2026-01-23 21:24</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
@@ -4548,25 +4548,25 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H37" s="3" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 16:49</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="H37" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-06 19:00</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>52.5</v>
+        <v>69.2</v>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 02:39</t>
+          <t>2026-02-20 10:05</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -4575,11 +4575,11 @@
         </is>
       </c>
       <c r="N37" s="6" t="n">
-        <v>66.90000000000001</v>
+        <v>33.9</v>
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>2026-03-07 00:06</t>
+          <t>2026-03-06 19:42</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
@@ -4588,11 +4588,11 @@
         </is>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>50.1</v>
+        <v>51.2</v>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>2026-03-21 00:12</t>
+          <t>2026-03-20 21:30</t>
         </is>
       </c>
       <c r="S37" s="6" t="inlineStr">
@@ -4604,17 +4604,17 @@
         <v>0</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>301.3</v>
+        <v>253</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t>D+</t>
+        <v>50.6</v>
+      </c>
+      <c r="X37" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -4644,38 +4644,38 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E38" s="3" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 12:32</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 02:23</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="E38" s="6" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 19:54</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-07 15:18</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 09:01</t>
+          <t>2026-02-19 14:16</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -4683,25 +4683,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N38" s="6" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="O38" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 21:06</t>
-        </is>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="N38" s="3" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:06</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>69.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 00:39</t>
+          <t>2026-03-19 11:17</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -4710,20 +4710,20 @@
         </is>
       </c>
       <c r="T38" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>372.1</v>
+        <v>261.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t>C+</t>
+        <v>52.4</v>
+      </c>
+      <c r="X38" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
@@ -4753,38 +4753,38 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E39" s="3" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 10:11</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-06 21:18</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="inlineStr">
+      <c r="E39" s="6" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 19:54</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
+      <c r="H39" s="3" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-06 16:54</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
       <c r="K39" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>51.4</v>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 13:27</t>
+          <t>2026-02-20 04:49</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -4793,11 +4793,11 @@
         </is>
       </c>
       <c r="N39" s="6" t="n">
-        <v>55.9</v>
+        <v>43.2</v>
       </c>
       <c r="O39" s="6" t="inlineStr">
         <is>
-          <t>2026-03-07 00:24</t>
+          <t>2026-03-06 21:54</t>
         </is>
       </c>
       <c r="P39" s="6" t="inlineStr">
@@ -4806,11 +4806,11 @@
         </is>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>51.1</v>
+        <v>40.8</v>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>2026-03-21 01:00</t>
+          <t>2026-03-20 20:06</t>
         </is>
       </c>
       <c r="S39" s="6" t="inlineStr">
@@ -4822,17 +4822,17 @@
         <v>0</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>331</v>
+        <v>221.3</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="X39" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>44.3</v>
+      </c>
+      <c r="X39" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -4863,11 +4863,11 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>47.9</v>
+        <v>61</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 19:31</t>
+          <t>2026-01-23 23:00</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -4876,11 +4876,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>55.4</v>
+        <v>57.6</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 16:52</t>
+          <t>2026-02-05 23:01</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -4889,11 +4889,11 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>72.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 16:33</t>
+          <t>2026-02-19 06:23</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -4902,11 +4902,11 @@
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>70.7</v>
+        <v>64.5</v>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 11:45</t>
+          <t>2026-03-05 22:06</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -4914,34 +4914,34 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="Q40" s="3" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-19 11:15</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="Q40" s="6" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-20 20:42</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="T40" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>338</v>
+        <v>321.1</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -4972,11 +4972,11 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>100</v>
+        <v>63.9</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23 08:04</t>
+          <t>2026-01-23 12:02</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -4985,11 +4985,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>82.8</v>
+        <v>54.4</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 13:25</t>
+          <t>2026-02-05 18:21</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -4998,11 +4998,11 @@
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>78.5</v>
+        <v>84.7</v>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 13:02</t>
+          <t>2026-02-20 02:15</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -5010,47 +5010,47 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N41" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 20:01</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-19 22:58</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N41" s="6" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="O41" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 11:24</t>
+        </is>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-20 20:36</t>
+        </is>
+      </c>
+      <c r="S41" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="T41" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>454.8</v>
+        <v>280.4</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="X41" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>56.1</v>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -5081,11 +5081,11 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>76.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 16:38</t>
+          <t>2026-01-22 22:44</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -5094,11 +5094,11 @@
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>77.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 20:37</t>
+          <t>2026-02-03 17:39</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -5107,11 +5107,11 @@
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>80.5</v>
+        <v>81</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 22:45</t>
+          <t>2026-02-18 20:14</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -5120,11 +5120,11 @@
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 16:43</t>
+          <t>2026-03-02 11:09</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -5133,11 +5133,11 @@
         </is>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>84.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:46</t>
+          <t>2026-03-19 09:16</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -5149,17 +5149,17 @@
         <v>0</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>400.1</v>
+        <v>396.6</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>80</v>
+        <v>79.3</v>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -5190,11 +5190,11 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>69.5</v>
+        <v>76.8</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 14:58</t>
+          <t>2026-01-19 17:40</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 11:17</t>
+          <t>2026-02-04 15:11</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -5216,11 +5216,11 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>95.5</v>
+        <v>87.5</v>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 22:44</t>
+          <t>2026-02-16 13:06</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -5229,11 +5229,11 @@
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>76.7</v>
+        <v>86</v>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 09:07</t>
+          <t>2026-03-03 13:57</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
@@ -5242,11 +5242,11 @@
         </is>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>80.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 16:46</t>
+          <t>2026-03-20 22:25</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -5255,20 +5255,20 @@
         </is>
       </c>
       <c r="T43" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>401.4</v>
+        <v>442.4</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t>B+</t>
+        <v>88.5</v>
+      </c>
+      <c r="X43" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -5295,15 +5295,15 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>فريق 4</t>
+          <t>فريق 1</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>78</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 18:05</t>
+          <t>2026-01-22 22:27</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -5312,11 +5312,11 @@
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 16:48</t>
+          <t>2026-02-04 20:18</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -5325,11 +5325,11 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>93.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 15:49</t>
+          <t>2026-02-18 20:06</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -5338,11 +5338,11 @@
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 09:22</t>
+          <t>2026-03-03 19:03</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -5351,11 +5351,11 @@
         </is>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>90.3</v>
+        <v>75.8</v>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 14:06</t>
+          <t>2026-03-19 15:12</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -5364,20 +5364,20 @@
         </is>
       </c>
       <c r="T44" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>446.5</v>
+        <v>385.8</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="X44" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>77.2</v>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
@@ -5408,11 +5408,11 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>76.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 16:38</t>
+          <t>2026-01-22 22:44</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -5421,11 +5421,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>77.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 20:37</t>
+          <t>2026-02-03 17:39</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -5434,11 +5434,11 @@
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>80.5</v>
+        <v>81</v>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 22:45</t>
+          <t>2026-02-18 20:14</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -5447,11 +5447,11 @@
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 16:43</t>
+          <t>2026-03-02 11:09</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -5460,11 +5460,11 @@
         </is>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>84.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:46</t>
+          <t>2026-03-19 09:16</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -5476,17 +5476,17 @@
         <v>0</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>400.1</v>
+        <v>396.6</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>80</v>
+        <v>79.3</v>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -5517,11 +5517,11 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>79.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 14:02</t>
+          <t>2026-01-22 11:00</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -5530,11 +5530,11 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>75.5</v>
+        <v>74.5</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 10:37</t>
+          <t>2026-02-04 12:29</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -5543,11 +5543,11 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>94.2</v>
+        <v>87.8</v>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 15:00</t>
+          <t>2026-02-19 14:25</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -5556,11 +5556,11 @@
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 12:40</t>
+          <t>2026-03-03 15:50</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -5569,11 +5569,11 @@
         </is>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>84.2</v>
+        <v>83.7</v>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 19:24</t>
+          <t>2026-03-20 12:19</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -5582,16 +5582,16 @@
         </is>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>416.7</v>
+        <v>420.8</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>83.3</v>
+        <v>84.2</v>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
@@ -5622,15 +5622,15 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>فريق 1</t>
+          <t>فريق 2</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>82.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 21:17</t>
+          <t>2026-01-20 15:02</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -5639,11 +5639,11 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>91.3</v>
+        <v>72.3</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 15:23</t>
+          <t>2026-02-05 21:42</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -5652,11 +5652,11 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>92</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 16:53</t>
+          <t>2026-02-17 17:02</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -5665,11 +5665,11 @@
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 18:05</t>
+          <t>2026-03-03 09:55</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
@@ -5678,11 +5678,11 @@
         </is>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 15:43</t>
+          <t>2026-03-20 22:11</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
@@ -5691,20 +5691,20 @@
         </is>
       </c>
       <c r="T47" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="U47" s="3" t="n">
-        <v>468.8</v>
+        <v>398.8</v>
       </c>
       <c r="V47" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W47" s="3" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="X47" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>79.8</v>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
@@ -5731,15 +5731,15 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>فريق 4</t>
+          <t>فريق 3</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>78</v>
+        <v>76.8</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 18:05</t>
+          <t>2026-01-19 17:40</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -5748,11 +5748,11 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 16:48</t>
+          <t>2026-02-04 15:11</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -5761,11 +5761,11 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>93.7</v>
+        <v>87.5</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 15:49</t>
+          <t>2026-02-16 13:06</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -5774,11 +5774,11 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 09:22</t>
+          <t>2026-03-03 13:57</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
@@ -5787,11 +5787,11 @@
         </is>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>90.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 14:06</t>
+          <t>2026-03-20 22:25</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -5800,16 +5800,16 @@
         </is>
       </c>
       <c r="T48" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>446.5</v>
+        <v>442.4</v>
       </c>
       <c r="V48" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W48" s="3" t="n">
-        <v>89.3</v>
+        <v>88.5</v>
       </c>
       <c r="X48" s="4" t="inlineStr">
         <is>
@@ -5844,11 +5844,11 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>79.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 14:02</t>
+          <t>2026-01-22 11:00</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -5857,11 +5857,11 @@
         </is>
       </c>
       <c r="H49" s="3" t="n">
-        <v>75.5</v>
+        <v>74.5</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 10:37</t>
+          <t>2026-02-04 12:29</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -5870,11 +5870,11 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>94.2</v>
+        <v>87.8</v>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 15:00</t>
+          <t>2026-02-19 14:25</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -5883,11 +5883,11 @@
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 12:40</t>
+          <t>2026-03-03 15:50</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
@@ -5896,11 +5896,11 @@
         </is>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>84.2</v>
+        <v>83.7</v>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 19:24</t>
+          <t>2026-03-20 12:19</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr">
@@ -5909,16 +5909,16 @@
         </is>
       </c>
       <c r="T49" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>416.7</v>
+        <v>420.8</v>
       </c>
       <c r="V49" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>83.3</v>
+        <v>84.2</v>
       </c>
       <c r="X49" s="3" t="inlineStr">
         <is>
@@ -5949,15 +5949,15 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>فريق 6</t>
+          <t>فريق 5</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>76.7</v>
+        <v>75.8</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 16:38</t>
+          <t>2026-01-22 11:00</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -5966,11 +5966,11 @@
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>77.5</v>
+        <v>74.5</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 20:37</t>
+          <t>2026-02-04 12:29</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -5979,11 +5979,11 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>80.5</v>
+        <v>87.8</v>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 22:45</t>
+          <t>2026-02-19 14:25</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -5992,11 +5992,11 @@
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 16:43</t>
+          <t>2026-03-03 15:50</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
@@ -6005,11 +6005,11 @@
         </is>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>84.5</v>
+        <v>83.7</v>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:46</t>
+          <t>2026-03-20 12:19</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
@@ -6018,16 +6018,16 @@
         </is>
       </c>
       <c r="T50" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U50" s="3" t="n">
-        <v>400.1</v>
+        <v>420.8</v>
       </c>
       <c r="V50" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W50" s="3" t="n">
-        <v>80</v>
+        <v>84.2</v>
       </c>
       <c r="X50" s="3" t="inlineStr">
         <is>
@@ -6058,15 +6058,15 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>فريق 4</t>
+          <t>فريق 3</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>78</v>
+        <v>76.8</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 18:05</t>
+          <t>2026-01-19 17:40</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -6075,11 +6075,11 @@
         </is>
       </c>
       <c r="H51" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 16:48</t>
+          <t>2026-02-04 15:11</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -6088,11 +6088,11 @@
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>93.7</v>
+        <v>87.5</v>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 15:49</t>
+          <t>2026-02-16 13:06</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -6101,11 +6101,11 @@
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 09:22</t>
+          <t>2026-03-03 13:57</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
@@ -6114,11 +6114,11 @@
         </is>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>90.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 14:06</t>
+          <t>2026-03-20 22:25</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -6127,16 +6127,16 @@
         </is>
       </c>
       <c r="T51" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>446.5</v>
+        <v>442.4</v>
       </c>
       <c r="V51" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>89.3</v>
+        <v>88.5</v>
       </c>
       <c r="X51" s="4" t="inlineStr">
         <is>
@@ -6167,15 +6167,15 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>فريق 2</t>
+          <t>فريق 4</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 11:59</t>
+          <t>2026-01-22 18:50</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -6184,11 +6184,11 @@
         </is>
       </c>
       <c r="H52" s="3" t="n">
-        <v>86.2</v>
+        <v>70.3</v>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 19:35</t>
+          <t>2026-02-04 12:51</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -6197,11 +6197,11 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 15:54</t>
+          <t>2026-02-16 15:09</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -6210,11 +6210,11 @@
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>81.3</v>
+        <v>85.8</v>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 13:08</t>
+          <t>2026-03-04 22:51</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -6223,11 +6223,11 @@
         </is>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>84.5</v>
+        <v>89</v>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 10:04</t>
+          <t>2026-03-20 12:55</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -6239,17 +6239,17 @@
         <v>15</v>
       </c>
       <c r="U52" s="3" t="n">
-        <v>434.5</v>
+        <v>415</v>
       </c>
       <c r="V52" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W52" s="3" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="X52" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>83</v>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y52" s="3" t="inlineStr">
@@ -6276,15 +6276,15 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>فريق 2</t>
+          <t>فريق 4</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 11:59</t>
+          <t>2026-01-22 18:50</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -6293,11 +6293,11 @@
         </is>
       </c>
       <c r="H53" s="3" t="n">
-        <v>86.2</v>
+        <v>70.3</v>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 19:35</t>
+          <t>2026-02-04 12:51</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -6306,11 +6306,11 @@
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 15:54</t>
+          <t>2026-02-16 15:09</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -6319,11 +6319,11 @@
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>81.3</v>
+        <v>85.8</v>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 13:08</t>
+          <t>2026-03-04 22:51</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
@@ -6332,11 +6332,11 @@
         </is>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>84.5</v>
+        <v>89</v>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 10:04</t>
+          <t>2026-03-20 12:55</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
@@ -6348,17 +6348,17 @@
         <v>15</v>
       </c>
       <c r="U53" s="3" t="n">
-        <v>434.5</v>
+        <v>415</v>
       </c>
       <c r="V53" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W53" s="3" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="X53" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>83</v>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y53" s="3" t="inlineStr">
@@ -6385,15 +6385,15 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>فريق 3</t>
+          <t>فريق 2</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>69.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 14:58</t>
+          <t>2026-01-20 15:02</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -6402,11 +6402,11 @@
         </is>
       </c>
       <c r="H54" s="3" t="n">
-        <v>79.2</v>
+        <v>72.3</v>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 11:17</t>
+          <t>2026-02-05 21:42</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -6415,11 +6415,11 @@
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>95.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 22:44</t>
+          <t>2026-02-17 17:02</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -6428,11 +6428,11 @@
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>76.7</v>
+        <v>88.7</v>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 09:07</t>
+          <t>2026-03-03 09:55</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
@@ -6441,11 +6441,11 @@
         </is>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>80.5</v>
+        <v>86.3</v>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 16:46</t>
+          <t>2026-03-20 22:11</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -6457,17 +6457,17 @@
         <v>0</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>401.4</v>
+        <v>398.8</v>
       </c>
       <c r="V54" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>80.3</v>
+        <v>79.8</v>
       </c>
       <c r="X54" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y54" s="3" t="inlineStr">
@@ -6498,11 +6498,11 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 11:59</t>
+          <t>2026-01-20 15:02</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -6511,11 +6511,11 @@
         </is>
       </c>
       <c r="H55" s="3" t="n">
-        <v>86.2</v>
+        <v>72.3</v>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 19:35</t>
+          <t>2026-02-05 21:42</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -6524,11 +6524,11 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 15:54</t>
+          <t>2026-02-17 17:02</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -6537,11 +6537,11 @@
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>81.3</v>
+        <v>88.7</v>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 13:08</t>
+          <t>2026-03-03 09:55</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
@@ -6550,11 +6550,11 @@
         </is>
       </c>
       <c r="Q55" s="3" t="n">
-        <v>84.5</v>
+        <v>86.3</v>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 10:04</t>
+          <t>2026-03-20 22:11</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr">
@@ -6563,20 +6563,20 @@
         </is>
       </c>
       <c r="T55" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>434.5</v>
+        <v>398.8</v>
       </c>
       <c r="V55" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W55" s="3" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="X55" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>79.8</v>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="Y55" s="3" t="inlineStr">
@@ -6603,15 +6603,15 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>فريق 3</t>
+          <t>فريق 1</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>69.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 14:58</t>
+          <t>2026-01-22 22:27</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -6620,11 +6620,11 @@
         </is>
       </c>
       <c r="H56" s="3" t="n">
-        <v>79.2</v>
+        <v>68.2</v>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 11:17</t>
+          <t>2026-02-04 20:18</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -6633,11 +6633,11 @@
         </is>
       </c>
       <c r="K56" s="3" t="n">
-        <v>95.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 22:44</t>
+          <t>2026-02-18 20:06</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -6646,11 +6646,11 @@
         </is>
       </c>
       <c r="N56" s="3" t="n">
-        <v>76.7</v>
+        <v>79.3</v>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 09:07</t>
+          <t>2026-03-03 19:03</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
@@ -6659,11 +6659,11 @@
         </is>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>80.5</v>
+        <v>75.8</v>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 16:46</t>
+          <t>2026-03-19 15:12</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr">
@@ -6675,17 +6675,17 @@
         <v>0</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>401.4</v>
+        <v>385.8</v>
       </c>
       <c r="V56" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>80.3</v>
+        <v>77.2</v>
       </c>
       <c r="X56" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y56" s="3" t="inlineStr">
@@ -6716,11 +6716,11 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>82.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 21:17</t>
+          <t>2026-01-22 22:27</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -6729,11 +6729,11 @@
         </is>
       </c>
       <c r="H57" s="3" t="n">
-        <v>91.3</v>
+        <v>68.2</v>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 15:23</t>
+          <t>2026-02-04 20:18</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -6742,11 +6742,11 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>92</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 16:53</t>
+          <t>2026-02-18 20:06</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -6755,11 +6755,11 @@
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 18:05</t>
+          <t>2026-03-03 19:03</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
@@ -6768,11 +6768,11 @@
         </is>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 15:43</t>
+          <t>2026-03-19 15:12</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
@@ -6781,20 +6781,20 @@
         </is>
       </c>
       <c r="T57" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="U57" s="3" t="n">
-        <v>468.8</v>
+        <v>385.8</v>
       </c>
       <c r="V57" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W57" s="3" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="X57" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>77.2</v>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="Y57" s="3" t="inlineStr">
@@ -6821,15 +6821,15 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>فريق 3</t>
+          <t>فريق 1</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>69.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 14:58</t>
+          <t>2026-01-22 22:27</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -6838,11 +6838,11 @@
         </is>
       </c>
       <c r="H58" s="3" t="n">
-        <v>79.2</v>
+        <v>68.2</v>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 11:17</t>
+          <t>2026-02-04 20:18</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -6851,11 +6851,11 @@
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>95.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 22:44</t>
+          <t>2026-02-18 20:06</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -6864,11 +6864,11 @@
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>76.7</v>
+        <v>79.3</v>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 09:07</t>
+          <t>2026-03-03 19:03</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
@@ -6877,11 +6877,11 @@
         </is>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>80.5</v>
+        <v>75.8</v>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 16:46</t>
+          <t>2026-03-19 15:12</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr">
@@ -6893,17 +6893,17 @@
         <v>0</v>
       </c>
       <c r="U58" s="3" t="n">
-        <v>401.4</v>
+        <v>385.8</v>
       </c>
       <c r="V58" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W58" s="3" t="n">
-        <v>80.3</v>
+        <v>77.2</v>
       </c>
       <c r="X58" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y58" s="3" t="inlineStr">
@@ -6934,11 +6934,11 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 11:59</t>
+          <t>2026-01-20 15:02</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -6947,11 +6947,11 @@
         </is>
       </c>
       <c r="H59" s="3" t="n">
-        <v>86.2</v>
+        <v>72.3</v>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 19:35</t>
+          <t>2026-02-05 21:42</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -6960,11 +6960,11 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 15:54</t>
+          <t>2026-02-17 17:02</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -6973,11 +6973,11 @@
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>81.3</v>
+        <v>88.7</v>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 13:08</t>
+          <t>2026-03-03 09:55</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
@@ -6986,11 +6986,11 @@
         </is>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>84.5</v>
+        <v>86.3</v>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 10:04</t>
+          <t>2026-03-20 22:11</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr">
@@ -6999,20 +6999,20 @@
         </is>
       </c>
       <c r="T59" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>434.5</v>
+        <v>398.8</v>
       </c>
       <c r="V59" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="X59" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>79.8</v>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
@@ -7039,15 +7039,15 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>فريق 1</t>
+          <t>فريق 5</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>82.3</v>
+        <v>75.8</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 21:17</t>
+          <t>2026-01-22 11:00</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -7056,11 +7056,11 @@
         </is>
       </c>
       <c r="H60" s="3" t="n">
-        <v>91.3</v>
+        <v>74.5</v>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 15:23</t>
+          <t>2026-02-04 12:29</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -7069,11 +7069,11 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>92</v>
+        <v>87.8</v>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 16:53</t>
+          <t>2026-02-19 14:25</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -7082,11 +7082,11 @@
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 18:05</t>
+          <t>2026-03-03 15:50</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
@@ -7095,11 +7095,11 @@
         </is>
       </c>
       <c r="Q60" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 15:43</t>
+          <t>2026-03-20 12:19</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr">
@@ -7108,20 +7108,20 @@
         </is>
       </c>
       <c r="T60" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="U60" s="3" t="n">
-        <v>468.8</v>
+        <v>420.8</v>
       </c>
       <c r="V60" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W60" s="3" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="X60" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>84.2</v>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y60" s="3" t="inlineStr">
@@ -7148,15 +7148,15 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>فريق 5</t>
+          <t>فريق 4</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>79.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 14:02</t>
+          <t>2026-01-22 18:50</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -7165,11 +7165,11 @@
         </is>
       </c>
       <c r="H61" s="3" t="n">
-        <v>75.5</v>
+        <v>70.3</v>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 10:37</t>
+          <t>2026-02-04 12:51</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -7178,11 +7178,11 @@
         </is>
       </c>
       <c r="K61" s="3" t="n">
-        <v>94.2</v>
+        <v>77.3</v>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 15:00</t>
+          <t>2026-02-16 15:09</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -7191,11 +7191,11 @@
         </is>
       </c>
       <c r="N61" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 12:40</t>
+          <t>2026-03-04 22:51</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
@@ -7204,11 +7204,11 @@
         </is>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>84.2</v>
+        <v>89</v>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 19:24</t>
+          <t>2026-03-20 12:55</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr">
@@ -7217,16 +7217,16 @@
         </is>
       </c>
       <c r="T61" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>416.7</v>
+        <v>415</v>
       </c>
       <c r="V61" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>83.3</v>
+        <v>83</v>
       </c>
       <c r="X61" s="3" t="inlineStr">
         <is>
@@ -7257,28 +7257,28 @@
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>فريق 6</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 20:38</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 5</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:06</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H62" s="3" t="n">
-        <v>66.7</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 11:04</t>
+          <t>2026-02-06 14:47</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -7287,11 +7287,11 @@
         </is>
       </c>
       <c r="K62" s="3" t="n">
-        <v>85.3</v>
+        <v>88.2</v>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 08:22</t>
+          <t>2026-02-19 06:52</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -7299,47 +7299,47 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N62" s="3" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="O62" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 09:36</t>
-        </is>
-      </c>
-      <c r="P62" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q62" s="3" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="R62" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-19 17:51</t>
-        </is>
-      </c>
-      <c r="S62" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N62" s="6" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="O62" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-06 20:30</t>
+        </is>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-20 18:00</t>
+        </is>
+      </c>
+      <c r="S62" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="T62" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U62" s="3" t="n">
-        <v>364.7</v>
+        <v>307.5</v>
       </c>
       <c r="V62" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W62" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y62" s="3" t="inlineStr">
@@ -7366,15 +7366,15 @@
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>فريق 4</t>
+          <t>فريق 2</t>
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>45.4</v>
+        <v>57.5</v>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>2026-01-24 00:12</t>
+          <t>2026-01-23 19:36</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
@@ -7383,11 +7383,11 @@
         </is>
       </c>
       <c r="H63" s="3" t="n">
-        <v>78.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 00:08</t>
+          <t>2026-02-05 19:43</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
@@ -7395,38 +7395,38 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K63" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="L63" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-21 00:18</t>
-        </is>
-      </c>
-      <c r="M63" s="6" t="inlineStr">
+      <c r="K63" s="3" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-19 20:09</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N63" s="6" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="O63" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 17:54</t>
+        </is>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="N63" s="6" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="O63" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 22:48</t>
-        </is>
-      </c>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
       <c r="Q63" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 09:37</t>
+          <t>2026-03-20 00:53</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr">
@@ -7438,17 +7438,17 @@
         <v>0</v>
       </c>
       <c r="U63" s="3" t="n">
-        <v>323.6</v>
+        <v>338.9</v>
       </c>
       <c r="V63" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W63" s="3" t="n">
-        <v>64.7</v>
+        <v>67.8</v>
       </c>
       <c r="X63" s="3" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y63" s="3" t="inlineStr">
@@ -7475,15 +7475,15 @@
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>فريق 2</t>
+          <t>فريق 3</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>79</v>
+        <v>76.8</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 22:02</t>
+          <t>2026-01-22 12:06</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -7492,11 +7492,11 @@
         </is>
       </c>
       <c r="H64" s="3" t="n">
-        <v>76</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 07:54</t>
+          <t>2026-02-05 11:44</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
@@ -7504,17 +7504,17 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K64" s="3" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-20 13:48</t>
-        </is>
-      </c>
-      <c r="M64" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="K64" s="6" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-20 22:12</t>
+        </is>
+      </c>
+      <c r="M64" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="N64" s="3" t="n">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 21:25</t>
+          <t>2026-03-05 19:34</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
@@ -7531,11 +7531,11 @@
         </is>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>81.2</v>
+        <v>80.8</v>
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 18:50</t>
+          <t>2026-03-20 04:26</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr">
@@ -7544,20 +7544,20 @@
         </is>
       </c>
       <c r="T64" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>434</v>
+        <v>408.5</v>
       </c>
       <c r="V64" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="X64" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>81.7</v>
+      </c>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
@@ -7584,15 +7584,15 @@
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>فريق 1</t>
+          <t>فريق 3</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>68.5</v>
+        <v>76.8</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23 07:11</t>
+          <t>2026-01-22 12:06</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -7601,11 +7601,11 @@
         </is>
       </c>
       <c r="H65" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 13:23</t>
+          <t>2026-02-05 11:44</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
@@ -7613,25 +7613,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K65" s="3" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="L65" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-19 18:05</t>
-        </is>
-      </c>
-      <c r="M65" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="K65" s="6" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-20 22:12</t>
+        </is>
+      </c>
+      <c r="M65" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="N65" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 06:17</t>
+          <t>2026-03-05 19:34</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
@@ -7640,11 +7640,11 @@
         </is>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 09:48</t>
+          <t>2026-03-20 04:26</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr">
@@ -7656,17 +7656,17 @@
         <v>20</v>
       </c>
       <c r="U65" s="3" t="n">
-        <v>426.5</v>
+        <v>408.5</v>
       </c>
       <c r="V65" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W65" s="3" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="X65" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>81.7</v>
+      </c>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y65" s="3" t="inlineStr">
@@ -7693,15 +7693,15 @@
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>فريق 5</t>
+          <t>فريق 3</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 14:31</t>
+          <t>2026-01-22 12:06</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -7710,11 +7710,11 @@
         </is>
       </c>
       <c r="H66" s="3" t="n">
-        <v>77.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 22:26</t>
+          <t>2026-02-05 11:44</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -7722,25 +7722,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K66" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-20 12:26</t>
-        </is>
-      </c>
-      <c r="M66" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="K66" s="6" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-20 22:12</t>
+        </is>
+      </c>
+      <c r="M66" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>83.2</v>
+        <v>87.3</v>
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 04:31</t>
+          <t>2026-03-05 19:34</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
@@ -7749,11 +7749,11 @@
         </is>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>77.8</v>
+        <v>80.8</v>
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 02:31</t>
+          <t>2026-03-20 04:26</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr">
@@ -7762,16 +7762,16 @@
         </is>
       </c>
       <c r="T66" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>413.3</v>
+        <v>408.5</v>
       </c>
       <c r="V66" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>82.7</v>
+        <v>81.7</v>
       </c>
       <c r="X66" s="3" t="inlineStr">
         <is>
@@ -7802,28 +7802,28 @@
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>فريق 6</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 20:38</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 4</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-24 15:36</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H67" s="3" t="n">
-        <v>66.7</v>
+        <v>79.2</v>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 11:04</t>
+          <t>2026-02-06 18:47</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -7832,11 +7832,11 @@
         </is>
       </c>
       <c r="K67" s="3" t="n">
-        <v>85.3</v>
+        <v>89.5</v>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 08:22</t>
+          <t>2026-02-19 21:40</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -7845,11 +7845,11 @@
         </is>
       </c>
       <c r="N67" s="3" t="n">
-        <v>68.5</v>
+        <v>83</v>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 09:36</t>
+          <t>2026-03-05 19:27</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
@@ -7858,11 +7858,11 @@
         </is>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:51</t>
+          <t>2026-03-19 18:44</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr">
@@ -7871,20 +7871,20 @@
         </is>
       </c>
       <c r="T67" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U67" s="3" t="n">
-        <v>364.7</v>
+        <v>386.3</v>
       </c>
       <c r="V67" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W67" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="X67" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y67" s="3" t="inlineStr">
@@ -7915,11 +7915,11 @@
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>45.4</v>
+        <v>30</v>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>2026-01-24 00:12</t>
+          <t>2026-01-24 15:36</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -7928,11 +7928,11 @@
         </is>
       </c>
       <c r="H68" s="3" t="n">
-        <v>78.2</v>
+        <v>79.2</v>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 00:08</t>
+          <t>2026-02-06 18:47</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -7940,38 +7940,38 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K68" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="L68" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-21 00:18</t>
-        </is>
-      </c>
-      <c r="M68" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="N68" s="6" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="O68" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 22:48</t>
-        </is>
-      </c>
-      <c r="P68" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="K68" s="3" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-19 21:40</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:27</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 09:37</t>
+          <t>2026-03-19 18:44</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr">
@@ -7980,20 +7980,20 @@
         </is>
       </c>
       <c r="T68" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U68" s="3" t="n">
-        <v>323.6</v>
+        <v>386.3</v>
       </c>
       <c r="V68" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W68" s="3" t="n">
-        <v>64.7</v>
+        <v>77.3</v>
       </c>
       <c r="X68" s="3" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y68" s="3" t="inlineStr">
@@ -8020,28 +8020,28 @@
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>فريق 1</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 07:11</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 5</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:06</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H69" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 13:23</t>
+          <t>2026-02-06 14:47</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -8050,11 +8050,11 @@
         </is>
       </c>
       <c r="K69" s="3" t="n">
-        <v>94.3</v>
+        <v>88.2</v>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 18:05</t>
+          <t>2026-02-19 06:52</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
@@ -8062,47 +8062,47 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N69" s="3" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 06:17</t>
-        </is>
-      </c>
-      <c r="P69" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q69" s="3" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="R69" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-19 09:48</t>
-        </is>
-      </c>
-      <c r="S69" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N69" s="6" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="O69" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-06 20:30</t>
+        </is>
+      </c>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="Q69" s="6" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-20 18:00</t>
+        </is>
+      </c>
+      <c r="S69" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="T69" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>426.5</v>
+        <v>307.5</v>
       </c>
       <c r="V69" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="X69" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>61.5</v>
+      </c>
+      <c r="X69" s="3" t="inlineStr">
+        <is>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y69" s="3" t="inlineStr">
@@ -8129,28 +8129,28 @@
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>فريق 6</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 20:38</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 5</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:06</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H70" s="3" t="n">
-        <v>66.7</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 11:04</t>
+          <t>2026-02-06 14:47</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -8159,11 +8159,11 @@
         </is>
       </c>
       <c r="K70" s="3" t="n">
-        <v>85.3</v>
+        <v>88.2</v>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 08:22</t>
+          <t>2026-02-19 06:52</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
@@ -8171,47 +8171,47 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N70" s="3" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="O70" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 09:36</t>
-        </is>
-      </c>
-      <c r="P70" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q70" s="3" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="R70" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-19 17:51</t>
-        </is>
-      </c>
-      <c r="S70" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N70" s="6" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="O70" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-06 20:30</t>
+        </is>
+      </c>
+      <c r="P70" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="Q70" s="6" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="R70" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-20 18:00</t>
+        </is>
+      </c>
+      <c r="S70" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="T70" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U70" s="3" t="n">
-        <v>364.7</v>
+        <v>307.5</v>
       </c>
       <c r="V70" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W70" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="X70" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y70" s="3" t="inlineStr">
@@ -8238,28 +8238,28 @@
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>فريق 1</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 07:11</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 2</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 19:36</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H71" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 13:23</t>
+          <t>2026-02-05 19:43</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
@@ -8268,11 +8268,11 @@
         </is>
       </c>
       <c r="K71" s="3" t="n">
-        <v>94.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 18:05</t>
+          <t>2026-02-19 20:09</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
@@ -8280,25 +8280,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N71" s="3" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="O71" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 06:17</t>
-        </is>
-      </c>
-      <c r="P71" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N71" s="6" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="O71" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 17:54</t>
+        </is>
+      </c>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 09:48</t>
+          <t>2026-03-20 00:53</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -8307,20 +8307,20 @@
         </is>
       </c>
       <c r="T71" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>426.5</v>
+        <v>338.9</v>
       </c>
       <c r="V71" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="X71" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>67.8</v>
+      </c>
+      <c r="X71" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="Y71" s="3" t="inlineStr">
@@ -8347,15 +8347,15 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>فريق 5</t>
+          <t>فريق 1</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 14:31</t>
+          <t>2026-01-23 00:24</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -8364,11 +8364,11 @@
         </is>
       </c>
       <c r="H72" s="3" t="n">
-        <v>77.3</v>
+        <v>79.3</v>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 22:26</t>
+          <t>2026-02-05 18:50</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -8377,11 +8377,11 @@
         </is>
       </c>
       <c r="K72" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 12:26</t>
+          <t>2026-02-18 11:28</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
@@ -8389,47 +8389,47 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N72" s="3" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="O72" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-06 04:31</t>
-        </is>
-      </c>
-      <c r="P72" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q72" s="3" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="R72" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-19 02:31</t>
-        </is>
-      </c>
-      <c r="S72" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N72" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="O72" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 17:48</t>
+        </is>
+      </c>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="Q72" s="6" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="R72" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-20 21:30</t>
+        </is>
+      </c>
+      <c r="S72" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="T72" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="n">
-        <v>413.3</v>
+        <v>322.6</v>
       </c>
       <c r="V72" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W72" s="3" t="n">
-        <v>82.7</v>
+        <v>64.5</v>
       </c>
       <c r="X72" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y72" s="3" t="inlineStr">
@@ -8456,28 +8456,28 @@
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>فريق 3</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 16:35</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 4</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-24 15:36</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H73" s="3" t="n">
-        <v>65.7</v>
+        <v>79.2</v>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 14:14</t>
+          <t>2026-02-06 18:47</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
@@ -8486,11 +8486,11 @@
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>81.5</v>
+        <v>89.5</v>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 12:26</t>
+          <t>2026-02-19 21:40</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
@@ -8499,11 +8499,11 @@
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 16:38</t>
+          <t>2026-03-05 19:27</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
@@ -8512,11 +8512,11 @@
         </is>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 06:05</t>
+          <t>2026-03-19 18:44</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr">
@@ -8525,20 +8525,20 @@
         </is>
       </c>
       <c r="T73" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U73" s="3" t="n">
-        <v>370.7</v>
+        <v>386.3</v>
       </c>
       <c r="V73" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W73" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="X73" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y73" s="3" t="inlineStr">
@@ -8565,67 +8565,67 @@
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>فريق 4</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-24 00:12</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
+          <t>فريق 3</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-22 12:06</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-05 11:44</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K74" s="6" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="L74" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-20 22:12</t>
+        </is>
+      </c>
+      <c r="M74" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H74" s="3" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 00:08</t>
-        </is>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K74" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="L74" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-21 00:18</t>
-        </is>
-      </c>
-      <c r="M74" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="N74" s="6" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="O74" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 22:48</t>
-        </is>
-      </c>
-      <c r="P74" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="N74" s="3" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-05 19:34</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 09:37</t>
+          <t>2026-03-20 04:26</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr">
@@ -8634,20 +8634,20 @@
         </is>
       </c>
       <c r="T74" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>323.6</v>
+        <v>408.5</v>
       </c>
       <c r="V74" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>64.7</v>
+        <v>81.7</v>
       </c>
       <c r="X74" s="3" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y74" s="3" t="inlineStr">
@@ -8674,15 +8674,15 @@
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>فريق 5</t>
+          <t>فريق 6</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 14:31</t>
+          <t>2026-01-23 05:32</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -8691,11 +8691,11 @@
         </is>
       </c>
       <c r="H75" s="3" t="n">
-        <v>77.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 22:26</t>
+          <t>2026-02-06 01:35</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -8704,11 +8704,11 @@
         </is>
       </c>
       <c r="K75" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 12:26</t>
+          <t>2026-02-20 06:50</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
@@ -8717,11 +8717,11 @@
         </is>
       </c>
       <c r="N75" s="3" t="n">
-        <v>83.2</v>
+        <v>93.2</v>
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 04:31</t>
+          <t>2026-03-05 13:03</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
@@ -8730,11 +8730,11 @@
         </is>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>77.8</v>
+        <v>96.2</v>
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 02:31</t>
+          <t>2026-03-20 08:15</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr">
@@ -8743,20 +8743,20 @@
         </is>
       </c>
       <c r="T75" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="U75" s="3" t="n">
-        <v>413.3</v>
+        <v>491.2</v>
       </c>
       <c r="V75" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W75" s="3" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="X75" s="3" t="inlineStr">
-        <is>
-          <t>B+</t>
+        <v>98.2</v>
+      </c>
+      <c r="X75" s="4" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
       <c r="Y75" s="3" t="inlineStr">
@@ -8783,28 +8783,28 @@
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>فريق 3</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 16:35</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 5</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:06</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H76" s="3" t="n">
-        <v>65.7</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 14:14</t>
+          <t>2026-02-06 14:47</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -8813,11 +8813,11 @@
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>81.5</v>
+        <v>88.2</v>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 12:26</t>
+          <t>2026-02-19 06:52</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -8825,47 +8825,47 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N76" s="3" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="O76" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-06 16:38</t>
-        </is>
-      </c>
-      <c r="P76" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q76" s="3" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="R76" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-19 06:05</t>
-        </is>
-      </c>
-      <c r="S76" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N76" s="6" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="O76" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-06 20:30</t>
+        </is>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="Q76" s="6" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="R76" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-20 18:00</t>
+        </is>
+      </c>
+      <c r="S76" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="T76" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>370.7</v>
+        <v>307.5</v>
       </c>
       <c r="V76" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="X76" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y76" s="3" t="inlineStr">
@@ -8892,28 +8892,28 @@
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>فريق 3</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 16:35</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 4</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-24 15:36</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H77" s="3" t="n">
-        <v>65.7</v>
+        <v>79.2</v>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 14:14</t>
+          <t>2026-02-06 18:47</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
@@ -8922,11 +8922,11 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>81.5</v>
+        <v>89.5</v>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 12:26</t>
+          <t>2026-02-19 21:40</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -8935,11 +8935,11 @@
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 16:38</t>
+          <t>2026-03-05 19:27</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
@@ -8948,11 +8948,11 @@
         </is>
       </c>
       <c r="Q77" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="R77" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 06:05</t>
+          <t>2026-03-19 18:44</t>
         </is>
       </c>
       <c r="S77" s="3" t="inlineStr">
@@ -8961,20 +8961,20 @@
         </is>
       </c>
       <c r="T77" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U77" s="3" t="n">
-        <v>370.7</v>
+        <v>386.3</v>
       </c>
       <c r="V77" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W77" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="X77" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y77" s="3" t="inlineStr">
@@ -9004,25 +9004,25 @@
           <t>فريق 2</t>
         </is>
       </c>
-      <c r="E78" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 22:02</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="E78" s="6" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 19:36</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H78" s="3" t="n">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 07:54</t>
+          <t>2026-02-05 19:43</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
@@ -9031,11 +9031,11 @@
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>85.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 13:48</t>
+          <t>2026-02-19 20:09</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
@@ -9043,25 +9043,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N78" s="3" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="O78" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 21:25</t>
-        </is>
-      </c>
-      <c r="P78" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N78" s="6" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="O78" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 17:54</t>
+        </is>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>81.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 18:50</t>
+          <t>2026-03-20 00:53</t>
         </is>
       </c>
       <c r="S78" s="3" t="inlineStr">
@@ -9070,20 +9070,20 @@
         </is>
       </c>
       <c r="T78" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="U78" s="3" t="n">
-        <v>434</v>
+        <v>338.9</v>
       </c>
       <c r="V78" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W78" s="3" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="X78" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>67.8</v>
+      </c>
+      <c r="X78" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="Y78" s="3" t="inlineStr">
@@ -9110,15 +9110,15 @@
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>فريق 2</t>
+          <t>فريق 6</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>79</v>
+        <v>90.3</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 22:02</t>
+          <t>2026-01-23 05:32</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -9127,11 +9127,11 @@
         </is>
       </c>
       <c r="H79" s="3" t="n">
-        <v>76</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 07:54</t>
+          <t>2026-02-06 01:35</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
@@ -9140,11 +9140,11 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>85.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 13:48</t>
+          <t>2026-02-20 06:50</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
@@ -9153,11 +9153,11 @@
         </is>
       </c>
       <c r="N79" s="3" t="n">
-        <v>87.3</v>
+        <v>93.2</v>
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 21:25</t>
+          <t>2026-03-05 13:03</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
@@ -9166,11 +9166,11 @@
         </is>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>81.2</v>
+        <v>96.2</v>
       </c>
       <c r="R79" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 18:50</t>
+          <t>2026-03-20 08:15</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr">
@@ -9182,17 +9182,17 @@
         <v>25</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>434</v>
+        <v>491.2</v>
       </c>
       <c r="V79" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>86.8</v>
+        <v>98.2</v>
       </c>
       <c r="X79" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="Y79" s="3" t="inlineStr">
@@ -9219,15 +9219,15 @@
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>فريق 6</t>
+          <t>فريق 1</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 20:38</t>
+          <t>2026-01-23 00:24</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -9236,11 +9236,11 @@
         </is>
       </c>
       <c r="H80" s="3" t="n">
-        <v>66.7</v>
+        <v>79.3</v>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 11:04</t>
+          <t>2026-02-05 18:50</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
@@ -9249,11 +9249,11 @@
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>85.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 08:22</t>
+          <t>2026-02-18 11:28</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -9261,47 +9261,47 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N80" s="3" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="O80" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 09:36</t>
-        </is>
-      </c>
-      <c r="P80" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q80" s="3" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="R80" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-19 17:51</t>
-        </is>
-      </c>
-      <c r="S80" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N80" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="O80" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 17:48</t>
+        </is>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="Q80" s="6" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="R80" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-20 21:30</t>
+        </is>
+      </c>
+      <c r="S80" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="T80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U80" s="3" t="n">
-        <v>364.7</v>
+        <v>322.6</v>
       </c>
       <c r="V80" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W80" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="X80" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y80" s="3" t="inlineStr">
@@ -9328,15 +9328,15 @@
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>فريق 3</t>
+          <t>فريق 1</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>69.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 16:35</t>
+          <t>2026-01-23 00:24</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -9345,11 +9345,11 @@
         </is>
       </c>
       <c r="H81" s="3" t="n">
-        <v>65.7</v>
+        <v>79.3</v>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 14:14</t>
+          <t>2026-02-05 18:50</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
@@ -9358,11 +9358,11 @@
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>81.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 12:26</t>
+          <t>2026-02-18 11:28</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
@@ -9370,47 +9370,47 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N81" s="3" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="O81" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-06 16:38</t>
-        </is>
-      </c>
-      <c r="P81" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q81" s="3" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="R81" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-19 06:05</t>
-        </is>
-      </c>
-      <c r="S81" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N81" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="O81" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 17:48</t>
+        </is>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="Q81" s="6" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="R81" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-20 21:30</t>
+        </is>
+      </c>
+      <c r="S81" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="T81" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U81" s="3" t="n">
-        <v>370.7</v>
+        <v>322.6</v>
       </c>
       <c r="V81" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W81" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="X81" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y81" s="3" t="inlineStr">
@@ -9441,11 +9441,11 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>62.8</v>
+        <v>59</v>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>2026-01-23 15:00</t>
+          <t>2026-01-21 10:02</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr">
@@ -9454,11 +9454,11 @@
         </is>
       </c>
       <c r="H82" s="11" t="n">
-        <v>45.2</v>
+        <v>57.8</v>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>2026-02-03 16:37</t>
+          <t>2026-02-05 10:57</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
@@ -9509,13 +9509,13 @@
         <v>0</v>
       </c>
       <c r="U82" s="11" t="n">
-        <v>108</v>
+        <v>116.8</v>
       </c>
       <c r="V82" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W82" s="11" t="n">
-        <v>21.6</v>
+        <v>23.4</v>
       </c>
       <c r="X82" s="12" t="inlineStr">
         <is>
@@ -9550,11 +9550,11 @@
         </is>
       </c>
       <c r="E83" s="11" t="n">
-        <v>63.6</v>
+        <v>64.5</v>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>2026-01-21 13:15</t>
+          <t>2026-01-22 12:15</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -9563,11 +9563,11 @@
         </is>
       </c>
       <c r="H83" s="11" t="n">
-        <v>56.6</v>
+        <v>49.1</v>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>2026-02-04 16:27</t>
+          <t>2026-02-04 13:45</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr">
@@ -9618,13 +9618,13 @@
         <v>0</v>
       </c>
       <c r="U83" s="11" t="n">
-        <v>120.2</v>
+        <v>113.6</v>
       </c>
       <c r="V83" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W83" s="11" t="n">
-        <v>24</v>
+        <v>22.7</v>
       </c>
       <c r="X83" s="12" t="inlineStr">
         <is>
@@ -9659,11 +9659,11 @@
         </is>
       </c>
       <c r="E84" s="11" t="n">
-        <v>75.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>2026-01-20 19:48</t>
+          <t>2026-01-19 17:58</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr">
@@ -9672,11 +9672,11 @@
         </is>
       </c>
       <c r="H84" s="11" t="n">
-        <v>73.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>2026-02-03 16:47</t>
+          <t>2026-02-05 17:04</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
@@ -9727,13 +9727,13 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="n">
-        <v>148.9</v>
+        <v>139.9</v>
       </c>
       <c r="V84" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W84" s="11" t="n">
-        <v>29.8</v>
+        <v>28</v>
       </c>
       <c r="X84" s="12" t="inlineStr">
         <is>
@@ -9747,45 +9747,45 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="inlineStr">
+      <c r="A85" s="13" t="inlineStr">
         <is>
           <t>STD-084</t>
         </is>
       </c>
-      <c r="B85" s="10" t="inlineStr">
+      <c r="B85" s="13" t="inlineStr">
         <is>
           <t>ميار حمدي</t>
         </is>
       </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="inlineStr">
+      <c r="C85" s="13" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="D85" s="13" t="inlineStr">
         <is>
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E85" s="11" t="n">
-        <v>63</v>
-      </c>
-      <c r="F85" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-20 17:19</t>
-        </is>
-      </c>
-      <c r="G85" s="11" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="E85" s="14" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F85" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:24</t>
+        </is>
+      </c>
+      <c r="G85" s="14" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H85" s="11" t="n">
-        <v>69.59999999999999</v>
+        <v>44.7</v>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>2026-02-03 21:01</t>
+          <t>2026-02-06 07:04</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr">
@@ -9836,13 +9836,13 @@
         <v>0</v>
       </c>
       <c r="U85" s="11" t="n">
-        <v>132.6</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="V85" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W85" s="11" t="n">
-        <v>26.5</v>
+        <v>14.3</v>
       </c>
       <c r="X85" s="12" t="inlineStr">
         <is>
@@ -9877,11 +9877,11 @@
         </is>
       </c>
       <c r="E86" s="14" t="n">
-        <v>33.7</v>
+        <v>35</v>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>2026-01-23 21:18</t>
+          <t>2026-01-23 22:06</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -9889,17 +9889,17 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H86" s="11" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="I86" s="11" t="inlineStr">
-        <is>
-          <t>2026-02-05 04:57</t>
-        </is>
-      </c>
-      <c r="J86" s="11" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="H86" s="14" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="I86" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-06 18:36</t>
+        </is>
+      </c>
+      <c r="J86" s="14" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="K86" s="11" t="n">
@@ -9945,13 +9945,13 @@
         <v>0</v>
       </c>
       <c r="U86" s="11" t="n">
-        <v>91.8</v>
+        <v>78.2</v>
       </c>
       <c r="V86" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W86" s="11" t="n">
-        <v>18.4</v>
+        <v>15.6</v>
       </c>
       <c r="X86" s="12" t="inlineStr">
         <is>
@@ -9985,25 +9985,25 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E87" s="14" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="F87" s="14" t="inlineStr">
-        <is>
-          <t>2026-01-24 01:48</t>
-        </is>
-      </c>
-      <c r="G87" s="14" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="E87" s="11" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>2026-01-23 06:37</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="H87" s="14" t="n">
-        <v>22.2</v>
+        <v>37.9</v>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
-          <t>2026-02-07 01:42</t>
+          <t>2026-02-06 20:30</t>
         </is>
       </c>
       <c r="J87" s="14" t="inlineStr">
@@ -10054,13 +10054,13 @@
         <v>0</v>
       </c>
       <c r="U87" s="11" t="n">
-        <v>49.1</v>
+        <v>95</v>
       </c>
       <c r="V87" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W87" s="11" t="n">
-        <v>9.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="X87" s="12" t="inlineStr">
         <is>
@@ -10095,11 +10095,11 @@
         </is>
       </c>
       <c r="E88" s="14" t="n">
-        <v>49.4</v>
+        <v>55.6</v>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>2026-01-23 21:42</t>
+          <t>2026-01-23 20:12</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -10108,11 +10108,11 @@
         </is>
       </c>
       <c r="H88" s="14" t="n">
-        <v>43.4</v>
+        <v>44.6</v>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>2026-02-06 22:24</t>
+          <t>2026-02-06 20:12</t>
         </is>
       </c>
       <c r="J88" s="14" t="inlineStr">
@@ -10163,13 +10163,13 @@
         <v>0</v>
       </c>
       <c r="U88" s="11" t="n">
-        <v>92.8</v>
+        <v>100.2</v>
       </c>
       <c r="V88" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W88" s="11" t="n">
-        <v>18.6</v>
+        <v>20</v>
       </c>
       <c r="X88" s="12" t="inlineStr">
         <is>
@@ -10203,25 +10203,25 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E89" s="11" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="F89" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-22 07:51</t>
-        </is>
-      </c>
-      <c r="G89" s="11" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="E89" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="F89" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-23 19:54</t>
+        </is>
+      </c>
+      <c r="G89" s="14" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H89" s="14" t="n">
-        <v>58.6</v>
+        <v>30</v>
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
-          <t>2026-02-06 20:42</t>
+          <t>2026-02-06 18:06</t>
         </is>
       </c>
       <c r="J89" s="14" t="inlineStr">
@@ -10272,13 +10272,13 @@
         <v>0</v>
       </c>
       <c r="U89" s="11" t="n">
-        <v>142.7</v>
+        <v>79</v>
       </c>
       <c r="V89" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W89" s="11" t="n">
-        <v>28.5</v>
+        <v>15.8</v>
       </c>
       <c r="X89" s="12" t="inlineStr">
         <is>
@@ -10313,11 +10313,11 @@
         </is>
       </c>
       <c r="E90" s="11" t="n">
-        <v>76.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>2026-01-22 16:38</t>
+          <t>2026-01-22 22:44</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr">
@@ -10326,11 +10326,11 @@
         </is>
       </c>
       <c r="H90" s="11" t="n">
-        <v>77.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>2026-02-05 20:37</t>
+          <t>2026-02-03 17:39</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr">
@@ -10381,13 +10381,13 @@
         <v>0</v>
       </c>
       <c r="U90" s="11" t="n">
-        <v>154.2</v>
+        <v>153.2</v>
       </c>
       <c r="V90" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W90" s="11" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="X90" s="12" t="inlineStr">
         <is>
@@ -10422,11 +10422,11 @@
         </is>
       </c>
       <c r="E91" s="11" t="n">
-        <v>78</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>2026-01-22 18:05</t>
+          <t>2026-01-22 18:50</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
@@ -10435,11 +10435,11 @@
         </is>
       </c>
       <c r="H91" s="11" t="n">
-        <v>85.40000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>2026-02-05 16:48</t>
+          <t>2026-02-04 12:51</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr">
@@ -10490,13 +10490,13 @@
         <v>0</v>
       </c>
       <c r="U91" s="11" t="n">
-        <v>163.4</v>
+        <v>147.9</v>
       </c>
       <c r="V91" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W91" s="11" t="n">
-        <v>32.7</v>
+        <v>29.6</v>
       </c>
       <c r="X91" s="12" t="inlineStr">
         <is>
@@ -10527,15 +10527,15 @@
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>فريق 5</t>
+          <t>فريق 3</t>
         </is>
       </c>
       <c r="E92" s="11" t="n">
-        <v>79.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>2026-01-20 14:02</t>
+          <t>2026-01-19 17:40</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr">
@@ -10544,11 +10544,11 @@
         </is>
       </c>
       <c r="H92" s="11" t="n">
-        <v>75.5</v>
+        <v>79.2</v>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>2026-02-04 10:37</t>
+          <t>2026-02-04 15:11</t>
         </is>
       </c>
       <c r="J92" s="11" t="inlineStr">
@@ -10599,13 +10599,13 @@
         <v>0</v>
       </c>
       <c r="U92" s="11" t="n">
-        <v>154.9</v>
+        <v>156</v>
       </c>
       <c r="V92" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W92" s="11" t="n">
-        <v>31</v>
+        <v>31.2</v>
       </c>
       <c r="X92" s="12" t="inlineStr">
         <is>
@@ -10619,32 +10619,32 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="15" t="inlineStr">
+      <c r="A93" s="16" t="inlineStr">
         <is>
           <t>STD-092</t>
         </is>
       </c>
-      <c r="B93" s="15" t="inlineStr">
+      <c r="B93" s="16" t="inlineStr">
         <is>
           <t>عزة طلعت</t>
         </is>
       </c>
-      <c r="C93" s="15" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="D93" s="15" t="inlineStr">
-        <is>
-          <t>فريق 1</t>
+      <c r="C93" s="16" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="D93" s="16" t="inlineStr">
+        <is>
+          <t>فريق 6</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
-        <v>82.3</v>
+        <v>90.3</v>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>2026-01-19 21:17</t>
+          <t>2026-01-23 05:32</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -10653,11 +10653,11 @@
         </is>
       </c>
       <c r="H93" s="11" t="n">
-        <v>91.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>2026-02-06 15:23</t>
+          <t>2026-02-06 01:35</t>
         </is>
       </c>
       <c r="J93" s="11" t="inlineStr">
@@ -10708,13 +10708,13 @@
         <v>0</v>
       </c>
       <c r="U93" s="11" t="n">
-        <v>173.6</v>
+        <v>177.4</v>
       </c>
       <c r="V93" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W93" s="11" t="n">
-        <v>34.7</v>
+        <v>35.5</v>
       </c>
       <c r="X93" s="12" t="inlineStr">
         <is>
@@ -10745,28 +10745,28 @@
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>فريق 4</t>
-        </is>
-      </c>
-      <c r="E94" s="14" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="F94" s="14" t="inlineStr">
-        <is>
-          <t>2026-01-24 00:12</t>
-        </is>
-      </c>
-      <c r="G94" s="14" t="inlineStr">
-        <is>
-          <t>نعم</t>
+          <t>فريق 1</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>2026-01-23 00:24</t>
+        </is>
+      </c>
+      <c r="G94" s="11" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="H94" s="11" t="n">
-        <v>78.2</v>
+        <v>79.3</v>
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
-          <t>2026-02-06 00:08</t>
+          <t>2026-02-05 18:50</t>
         </is>
       </c>
       <c r="J94" s="11" t="inlineStr">
@@ -10817,13 +10817,13 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="n">
-        <v>123.6</v>
+        <v>155.4</v>
       </c>
       <c r="V94" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W94" s="11" t="n">
-        <v>24.7</v>
+        <v>31.1</v>
       </c>
       <c r="X94" s="12" t="inlineStr">
         <is>
@@ -10854,33 +10854,33 @@
       </c>
       <c r="D95" s="16" t="inlineStr">
         <is>
-          <t>فريق 2</t>
-        </is>
-      </c>
-      <c r="E95" s="11" t="n">
-        <v>79</v>
-      </c>
-      <c r="F95" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-22 22:02</t>
-        </is>
-      </c>
-      <c r="G95" s="11" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H95" s="11" t="n">
-        <v>76</v>
-      </c>
-      <c r="I95" s="11" t="inlineStr">
-        <is>
-          <t>2026-02-05 07:54</t>
-        </is>
-      </c>
-      <c r="J95" s="11" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 7</t>
+        </is>
+      </c>
+      <c r="E95" s="14" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="F95" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-23 19:54</t>
+        </is>
+      </c>
+      <c r="G95" s="14" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H95" s="14" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="I95" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-06 21:54</t>
+        </is>
+      </c>
+      <c r="J95" s="14" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="K95" s="11" t="n">
@@ -10926,13 +10926,13 @@
         <v>0</v>
       </c>
       <c r="U95" s="11" t="n">
-        <v>155</v>
+        <v>89.8</v>
       </c>
       <c r="V95" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W95" s="11" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="X95" s="12" t="inlineStr">
         <is>
@@ -10963,28 +10963,28 @@
       </c>
       <c r="D96" s="16" t="inlineStr">
         <is>
-          <t>فريق 5</t>
-        </is>
-      </c>
-      <c r="E96" s="11" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="F96" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-22 14:31</t>
-        </is>
-      </c>
-      <c r="G96" s="11" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 2</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="F96" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-23 19:36</t>
+        </is>
+      </c>
+      <c r="G96" s="14" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H96" s="11" t="n">
-        <v>77.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>2026-02-06 22:26</t>
+          <t>2026-02-05 19:43</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr">
@@ -11035,13 +11035,13 @@
         <v>0</v>
       </c>
       <c r="U96" s="11" t="n">
-        <v>155.9</v>
+        <v>140.1</v>
       </c>
       <c r="V96" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W96" s="11" t="n">
-        <v>31.2</v>
+        <v>28</v>
       </c>
       <c r="X96" s="12" t="inlineStr">
         <is>
@@ -11072,15 +11072,15 @@
       </c>
       <c r="D97" s="16" t="inlineStr">
         <is>
-          <t>فريق 1</t>
+          <t>فريق 6</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
-        <v>68.5</v>
+        <v>90.3</v>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>2026-01-23 07:11</t>
+          <t>2026-01-23 05:32</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -11089,11 +11089,11 @@
         </is>
       </c>
       <c r="H97" s="11" t="n">
-        <v>75.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>2026-02-05 13:23</t>
+          <t>2026-02-06 01:35</t>
         </is>
       </c>
       <c r="J97" s="11" t="inlineStr">
@@ -11144,13 +11144,13 @@
         <v>0</v>
       </c>
       <c r="U97" s="11" t="n">
-        <v>144.4</v>
+        <v>177.4</v>
       </c>
       <c r="V97" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W97" s="11" t="n">
-        <v>28.9</v>
+        <v>35.5</v>
       </c>
       <c r="X97" s="12" t="inlineStr">
         <is>
@@ -11265,31 +11265,31 @@
         </is>
       </c>
       <c r="C2" s="18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" s="18" t="n">
         <v>20</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>71</v>
+        <v>70.42</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>70.73999999999999</v>
+        <v>70.67</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>62.34</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>65.86</v>
+        <v>69</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>64.62</v>
+        <v>67.92</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>337.47</v>
+        <v>346.13</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>67.48999999999999</v>
+        <v>69.23</v>
       </c>
       <c r="L2" s="18" t="n">
         <v>0</v>
@@ -11307,34 +11307,34 @@
         </is>
       </c>
       <c r="C3" s="19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" s="19" t="n">
         <v>20</v>
       </c>
       <c r="E3" s="19" t="n">
-        <v>63.13</v>
+        <v>56.18</v>
       </c>
       <c r="F3" s="19" t="n">
-        <v>64</v>
+        <v>54.78</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>56.78</v>
+        <v>52.55</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>57.45</v>
+        <v>45.98</v>
       </c>
       <c r="I3" s="19" t="n">
-        <v>60.73</v>
+        <v>53.94</v>
       </c>
       <c r="J3" s="19" t="n">
-        <v>308.13</v>
+        <v>269.22</v>
       </c>
       <c r="K3" s="19" t="n">
-        <v>61.63</v>
+        <v>53.85</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
@@ -11349,31 +11349,31 @@
         </is>
       </c>
       <c r="C4" s="20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" s="20" t="n">
         <v>20</v>
       </c>
       <c r="E4" s="20" t="n">
-        <v>77.38</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F4" s="20" t="n">
-        <v>82.52</v>
+        <v>73.58</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>75.81999999999999</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="H4" s="20" t="n">
-        <v>66.77</v>
+        <v>71.97</v>
       </c>
       <c r="I4" s="20" t="n">
-        <v>72.14</v>
+        <v>73.33</v>
       </c>
       <c r="J4" s="20" t="n">
-        <v>382.75</v>
+        <v>375.83</v>
       </c>
       <c r="K4" s="20" t="n">
-        <v>76.55</v>
+        <v>75.19</v>
       </c>
       <c r="L4" s="20" t="n">
         <v>0</v>
@@ -11391,34 +11391,34 @@
         </is>
       </c>
       <c r="C5" s="21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="21" t="n">
         <v>20</v>
       </c>
       <c r="E5" s="21" t="n">
-        <v>68.48</v>
+        <v>62.48</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>73.3</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>67.58</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="H5" s="21" t="n">
-        <v>62.6</v>
+        <v>51.53</v>
       </c>
       <c r="I5" s="21" t="n">
-        <v>66.91</v>
+        <v>57.28</v>
       </c>
       <c r="J5" s="21" t="n">
-        <v>346.36</v>
+        <v>324.65</v>
       </c>
       <c r="K5" s="21" t="n">
-        <v>69.26000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="L5" s="21" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
